--- a/00_database_attends.xlsx
+++ b/00_database_attends.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/722ab3a21b3559f4/ドキュメント/2501_プロジェクト_研修会/seminar-management-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{667ACFDC-EB15-445D-8189-998BE2038D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{370953DC-32B8-491D-8089-03D154B1DCD7}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{667ACFDC-EB15-445D-8189-998BE2038D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40820496-CE08-4E9E-84E6-95DCA9D45A8A}"/>
   <bookViews>
-    <workbookView xWindow="-28770" yWindow="750" windowWidth="28770" windowHeight="15450" xr2:uid="{7E120885-D2B4-4B9A-84E8-C5BAE4A5FD4D}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E120885-D2B4-4B9A-84E8-C5BAE4A5FD4D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -100,10 +100,6 @@
     <t>time_per</t>
   </si>
   <si>
-    <t>attend_2026</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>修了証書交付</t>
     <rPh sb="0" eb="4">
       <t>シュウリョウショウショ</t>
@@ -232,6 +228,10 @@
   </si>
   <si>
     <t>j@scchr.jp</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>attend</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -338,6 +338,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -723,10 +727,10 @@
         <v>18</v>
       </c>
       <c r="T1" t="s">
+        <v>47</v>
+      </c>
+      <c r="U1" t="s">
         <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.15">
@@ -740,31 +744,31 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
         <v>21</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>22</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" t="s">
         <v>23</v>
       </c>
-      <c r="G2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>24</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>26</v>
-      </c>
-      <c r="L2" t="s">
-        <v>27</v>
       </c>
       <c r="M2" s="1">
         <v>46164.729166666664</v>
@@ -776,7 +780,7 @@
         <v>22</v>
       </c>
       <c r="P2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q2" s="3">
         <v>0.73402777777777772</v>
@@ -806,31 +810,31 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
         <v>21</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>22</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
       <c r="I3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" t="s">
         <v>26</v>
-      </c>
-      <c r="L3" t="s">
-        <v>27</v>
       </c>
       <c r="M3" s="1">
         <v>46164.729166666664</v>
@@ -842,7 +846,7 @@
         <v>17</v>
       </c>
       <c r="P3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q3" s="3">
         <v>0.7319444444444444</v>
@@ -869,31 +873,31 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
         <v>21</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>22</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" t="s">
         <v>23</v>
       </c>
-      <c r="G4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
       <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K4" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>32</v>
-      </c>
-      <c r="L4" t="s">
-        <v>33</v>
       </c>
       <c r="M4" s="1">
         <v>46164.729166666664</v>
@@ -905,7 +909,7 @@
         <v>8</v>
       </c>
       <c r="P4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q4" s="3">
         <v>0.72916666666666663</v>
@@ -932,31 +936,31 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
         <v>21</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>22</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" t="s">
         <v>23</v>
       </c>
-      <c r="G5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" t="s">
-        <v>24</v>
-      </c>
       <c r="I5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" t="s">
         <v>32</v>
-      </c>
-      <c r="L5" t="s">
-        <v>33</v>
       </c>
       <c r="M5" s="1">
         <v>46164.729166666664</v>
@@ -968,7 +972,7 @@
         <v>10</v>
       </c>
       <c r="P5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q5" s="3">
         <v>0.72916666666666663</v>
@@ -995,31 +999,31 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
         <v>21</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>22</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" t="s">
         <v>23</v>
       </c>
-      <c r="G6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" t="s">
-        <v>24</v>
-      </c>
       <c r="I6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>36</v>
-      </c>
-      <c r="L6" t="s">
-        <v>37</v>
       </c>
       <c r="M6" s="1">
         <v>46164.729166666664</v>
@@ -1031,7 +1035,7 @@
         <v>8</v>
       </c>
       <c r="P6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q6" s="3">
         <v>0.72916666666666663</v>

--- a/00_database_attends.xlsx
+++ b/00_database_attends.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/722ab3a21b3559f4/ドキュメント/2501_プロジェクト_研修会/seminar-management-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{667ACFDC-EB15-445D-8189-998BE2038D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40820496-CE08-4E9E-84E6-95DCA9D45A8A}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{667ACFDC-EB15-445D-8189-998BE2038D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5198661-9715-47E1-874F-9FA5ADC27706}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E120885-D2B4-4B9A-84E8-C5BAE4A5FD4D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="66">
   <si>
     <t>#</t>
     <phoneticPr fontId="2"/>
@@ -232,6 +232,86 @@
   </si>
   <si>
     <t>attend</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>東北大学病院</t>
+  </si>
+  <si>
+    <t>臨床研究監理センター</t>
+  </si>
+  <si>
+    <t>平塚市民病院</t>
+  </si>
+  <si>
+    <t>外科病棟</t>
+  </si>
+  <si>
+    <t>横浜市立大学附属病院</t>
+  </si>
+  <si>
+    <t>次世代臨床研究センター</t>
+  </si>
+  <si>
+    <t>横浜臨床研究ネットワーク</t>
+  </si>
+  <si>
+    <t>京都府立医科大学</t>
+  </si>
+  <si>
+    <t>呼吸器内科</t>
+  </si>
+  <si>
+    <t>三枝 弥生</t>
+    <rPh sb="0" eb="2">
+      <t>サエグサ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヤヨイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>岡本 陽子</t>
+    <rPh sb="3" eb="5">
+      <t>ヨウコ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>柴田 勝家</t>
+    <rPh sb="3" eb="5">
+      <t>カツイエ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>西元 太郎</t>
+    <rPh sb="1" eb="2">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>タロウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>m@tohoku.ac.jp</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>o@gmail.com</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>s@yokohama-cu.ac.jp</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>g@gmail.com</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -661,7 +741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A01A903D-398F-4617-8446-9AD2A9AC3E3B}">
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
@@ -1051,6 +1131,254 @@
         <v>1</v>
       </c>
     </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>260522</v>
+      </c>
+      <c r="C7">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="K7" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M7">
+        <v>46164.729166666664</v>
+      </c>
+      <c r="N7">
+        <v>46154.674305555556</v>
+      </c>
+      <c r="O7">
+        <v>10</v>
+      </c>
+      <c r="P7" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q7">
+        <v>0.74027777777777781</v>
+      </c>
+      <c r="R7">
+        <v>4.6527777777777779E-2</v>
+      </c>
+      <c r="S7">
+        <v>0.80722891566265054</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>260522</v>
+      </c>
+      <c r="C8">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="K8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8">
+        <v>46164.729166666664</v>
+      </c>
+      <c r="N8">
+        <v>46152.904861111114</v>
+      </c>
+      <c r="O8">
+        <v>11</v>
+      </c>
+      <c r="P8" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q8">
+        <v>0.74236111111111114</v>
+      </c>
+      <c r="R8">
+        <v>4.4444444444444446E-2</v>
+      </c>
+      <c r="S8">
+        <v>0.77108433734939752</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>260522</v>
+      </c>
+      <c r="C9">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="K9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" t="s">
+        <v>36</v>
+      </c>
+      <c r="M9">
+        <v>46164.729166666664</v>
+      </c>
+      <c r="N9">
+        <v>46150.661805555559</v>
+      </c>
+      <c r="O9">
+        <v>14</v>
+      </c>
+      <c r="P9" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q9">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="R9">
+        <v>4.6527777777777779E-2</v>
+      </c>
+      <c r="S9">
+        <v>0.80722891566265054</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>260522</v>
+      </c>
+      <c r="C10">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="K10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10">
+        <v>46164.729166666664</v>
+      </c>
+      <c r="N10">
+        <v>46151.007638888892</v>
+      </c>
+      <c r="O10">
+        <v>13</v>
+      </c>
+      <c r="P10" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q10">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="R10">
+        <v>6.0416666666666667E-2</v>
+      </c>
+      <c r="S10">
+        <v>1.0481927710843373</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <hyperlinks>
@@ -1059,6 +1387,10 @@
     <hyperlink ref="J4" r:id="rId3" xr:uid="{C8590C63-DE69-44CB-8AF3-80D9B12166EE}"/>
     <hyperlink ref="J5" r:id="rId4" xr:uid="{96C6DB18-5ACF-4377-B6AF-1D90BEEC67D4}"/>
     <hyperlink ref="J6" r:id="rId5" xr:uid="{B9507427-9EAB-4082-B489-11E43DF56A0F}"/>
+    <hyperlink ref="J7" r:id="rId6" xr:uid="{84AEC207-9759-419C-B64F-640BD04E2BCC}"/>
+    <hyperlink ref="J8" r:id="rId7" xr:uid="{0354F255-BAA7-48C2-B959-907148B8ADFE}"/>
+    <hyperlink ref="J9" r:id="rId8" xr:uid="{642082CD-893F-4A74-B27B-F043150D747D}"/>
+    <hyperlink ref="J10" r:id="rId9" xr:uid="{8B9BE1D5-5BC2-4E90-BC12-77CC0F574A4B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/00_database_attends.xlsx
+++ b/00_database_attends.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/722ab3a21b3559f4/ドキュメント/2501_プロジェクト_研修会/seminar-management-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{667ACFDC-EB15-445D-8189-998BE2038D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5198661-9715-47E1-874F-9FA5ADC27706}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{667ACFDC-EB15-445D-8189-998BE2038D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E848D2A-0BD9-4F00-9A10-EA4D634F325C}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7E120885-D2B4-4B9A-84E8-C5BAE4A5FD4D}"/>
   </bookViews>
@@ -399,7 +399,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -746,6 +746,7 @@
   <cols>
     <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="27.25" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.15">
@@ -809,7 +810,7 @@
       <c r="T1" t="s">
         <v>47</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="6" t="s">
         <v>19</v>
       </c>
     </row>
@@ -876,7 +877,7 @@
         <v>1</v>
       </c>
       <c r="U2" s="6">
-        <v>46164</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.15">
